--- a/artfynd/A 32322-2022 artfynd.xlsx
+++ b/artfynd/A 32322-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 32322-2022 artfynd.xlsx
+++ b/artfynd/A 32322-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY64"/>
+  <dimension ref="A1:AY60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7311,434 +7311,6 @@
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
-    <row r="61">
-      <c r="A61" t="n">
-        <v>112605769</v>
-      </c>
-      <c r="B61" t="n">
-        <v>81593</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E61" t="n">
-        <v>1312</v>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>Gammelgransskål</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>Pseudographis pinicola</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="P61" t="inlineStr">
-        <is>
-          <t>Kåpponis, Lu lm</t>
-        </is>
-      </c>
-      <c r="Q61" t="n">
-        <v>733661</v>
-      </c>
-      <c r="R61" t="n">
-        <v>7366951</v>
-      </c>
-      <c r="S61" t="n">
-        <v>10</v>
-      </c>
-      <c r="T61" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U61" t="inlineStr">
-        <is>
-          <t>Jokkmokk</t>
-        </is>
-      </c>
-      <c r="V61" t="inlineStr">
-        <is>
-          <t>Lule lappmark</t>
-        </is>
-      </c>
-      <c r="W61" t="inlineStr">
-        <is>
-          <t>Jokkmokk</t>
-        </is>
-      </c>
-      <c r="Y61" t="inlineStr">
-        <is>
-          <t>2022-10-21</t>
-        </is>
-      </c>
-      <c r="AA61" t="inlineStr">
-        <is>
-          <t>2022-10-21</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD61" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE61" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG61" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT61" t="inlineStr"/>
-      <c r="AW61" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX61" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY61" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" t="n">
-        <v>112605767</v>
-      </c>
-      <c r="B62" t="n">
-        <v>90331</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E62" t="n">
-        <v>760</v>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>Doftticka</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>Haploporus odorus</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
-      <c r="P62" t="inlineStr">
-        <is>
-          <t>Kåpponis, Lu lm</t>
-        </is>
-      </c>
-      <c r="Q62" t="n">
-        <v>733555</v>
-      </c>
-      <c r="R62" t="n">
-        <v>7366597</v>
-      </c>
-      <c r="S62" t="n">
-        <v>10</v>
-      </c>
-      <c r="T62" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U62" t="inlineStr">
-        <is>
-          <t>Jokkmokk</t>
-        </is>
-      </c>
-      <c r="V62" t="inlineStr">
-        <is>
-          <t>Lule lappmark</t>
-        </is>
-      </c>
-      <c r="W62" t="inlineStr">
-        <is>
-          <t>Jokkmokk</t>
-        </is>
-      </c>
-      <c r="Y62" t="inlineStr">
-        <is>
-          <t>2022-10-21</t>
-        </is>
-      </c>
-      <c r="AA62" t="inlineStr">
-        <is>
-          <t>2022-10-21</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD62" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE62" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG62" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT62" t="inlineStr"/>
-      <c r="AW62" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX62" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY62" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" t="n">
-        <v>112605768</v>
-      </c>
-      <c r="B63" t="n">
-        <v>77937</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E63" t="n">
-        <v>864</v>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Knottrig blåslav</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>Hypogymnia bitteri</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>(Lynge) Ahti</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
-      <c r="P63" t="inlineStr">
-        <is>
-          <t>Kåpponis, Lu lm</t>
-        </is>
-      </c>
-      <c r="Q63" t="n">
-        <v>733661</v>
-      </c>
-      <c r="R63" t="n">
-        <v>7366950</v>
-      </c>
-      <c r="S63" t="n">
-        <v>10</v>
-      </c>
-      <c r="T63" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U63" t="inlineStr">
-        <is>
-          <t>Jokkmokk</t>
-        </is>
-      </c>
-      <c r="V63" t="inlineStr">
-        <is>
-          <t>Lule lappmark</t>
-        </is>
-      </c>
-      <c r="W63" t="inlineStr">
-        <is>
-          <t>Jokkmokk</t>
-        </is>
-      </c>
-      <c r="Y63" t="inlineStr">
-        <is>
-          <t>2022-10-21</t>
-        </is>
-      </c>
-      <c r="AA63" t="inlineStr">
-        <is>
-          <t>2022-10-21</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD63" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE63" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG63" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT63" t="inlineStr"/>
-      <c r="AW63" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX63" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY63" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" t="n">
-        <v>112605766</v>
-      </c>
-      <c r="B64" t="n">
-        <v>90331</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E64" t="n">
-        <v>760</v>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Doftticka</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>Haploporus odorus</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="P64" t="inlineStr">
-        <is>
-          <t>Kåpponis, Lu lm</t>
-        </is>
-      </c>
-      <c r="Q64" t="n">
-        <v>733567</v>
-      </c>
-      <c r="R64" t="n">
-        <v>7366608</v>
-      </c>
-      <c r="S64" t="n">
-        <v>10</v>
-      </c>
-      <c r="T64" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U64" t="inlineStr">
-        <is>
-          <t>Jokkmokk</t>
-        </is>
-      </c>
-      <c r="V64" t="inlineStr">
-        <is>
-          <t>Lule lappmark</t>
-        </is>
-      </c>
-      <c r="W64" t="inlineStr">
-        <is>
-          <t>Jokkmokk</t>
-        </is>
-      </c>
-      <c r="Y64" t="inlineStr">
-        <is>
-          <t>2022-10-21</t>
-        </is>
-      </c>
-      <c r="AA64" t="inlineStr">
-        <is>
-          <t>2022-10-21</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD64" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE64" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG64" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT64" t="inlineStr"/>
-      <c r="AW64" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX64" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY64" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 32322-2022 artfynd.xlsx
+++ b/artfynd/A 32322-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY60"/>
+  <dimension ref="A1:AY62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>103467918</v>
+        <v>112605766</v>
       </c>
       <c r="B2" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92509</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>864</v>
+        <v>760</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>733779.1962848642</v>
+        <v>733567</v>
       </c>
       <c r="R2" t="n">
-        <v>7366958.519675439</v>
+        <v>7366608</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-09-09</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-09-09</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-21</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,49 +765,44 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>103467889</v>
+        <v>112605767</v>
       </c>
       <c r="B3" t="n">
-        <v>95525</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92509</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221941</v>
+        <v>760</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,13 +812,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>733835.820012884</v>
+        <v>733555</v>
       </c>
       <c r="R3" t="n">
-        <v>7366914.424980779</v>
+        <v>7366597</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,22 +842,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-09-09</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-09-09</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-21</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,49 +867,44 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>103467946</v>
+        <v>103467918</v>
       </c>
       <c r="B4" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6463</v>
+        <v>864</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>733721.1516755822</v>
+        <v>733779</v>
       </c>
       <c r="R4" t="n">
-        <v>7366952.044970254</v>
+        <v>7366959</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -972,19 +947,9 @@
           <t>2022-09-09</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-09-09</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,15 +976,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>103467942</v>
+        <v>112605768</v>
       </c>
       <c r="B5" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,21 +987,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>864</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,13 +1011,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>733784.0110811807</v>
+        <v>733661</v>
       </c>
       <c r="R5" t="n">
-        <v>7366958.922889399</v>
+        <v>7366950</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1081,22 +1041,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-09-09</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-21</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-09-09</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-21</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,27 +1066,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>103467890</v>
+        <v>103467874</v>
       </c>
       <c r="B6" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1139,21 +1089,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>733621.6059597323</v>
+        <v>733911</v>
       </c>
       <c r="R6" t="n">
-        <v>7366707.592837562</v>
+        <v>7366887</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1196,19 +1146,9 @@
           <t>2022-09-09</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-09-09</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,37 +1175,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>103467878</v>
+        <v>103467942</v>
       </c>
       <c r="B7" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1210,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>733648.4638170282</v>
+        <v>733784</v>
       </c>
       <c r="R7" t="n">
-        <v>7366937.080918693</v>
+        <v>7366959</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1308,19 +1243,9 @@
           <t>2022-09-09</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-09-09</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,37 +1272,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>103467908</v>
+        <v>112605769</v>
       </c>
       <c r="B8" t="n">
-        <v>78603</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6464</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,13 +1307,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>733857.5877405566</v>
+        <v>733661</v>
       </c>
       <c r="R8" t="n">
-        <v>7367011.500335538</v>
+        <v>7366951</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1417,22 +1337,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-09-09</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-21</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-09-09</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-21</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1447,49 +1362,44 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>103467950</v>
+        <v>103467882</v>
       </c>
       <c r="B9" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1409,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>733934.4438137778</v>
+        <v>733640</v>
       </c>
       <c r="R9" t="n">
-        <v>7366870.620544679</v>
+        <v>7366836</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1532,19 +1442,9 @@
           <t>2022-09-09</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-09-09</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,37 +1471,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>103467907</v>
+        <v>103467883</v>
       </c>
       <c r="B10" t="n">
-        <v>78603</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1611,10 +1506,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>733719.2111824828</v>
+        <v>733904</v>
       </c>
       <c r="R10" t="n">
-        <v>7366955.918584504</v>
+        <v>7366920</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1644,19 +1539,9 @@
           <t>2022-09-09</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-09-09</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,37 +1568,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>103467902</v>
+        <v>103467921</v>
       </c>
       <c r="B11" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1723,10 +1603,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>733641.3850557586</v>
+        <v>733641</v>
       </c>
       <c r="R11" t="n">
-        <v>7366645.068445551</v>
+        <v>7366645</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1756,19 +1636,9 @@
           <t>2022-09-09</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2022-09-09</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,37 +1665,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>103467906</v>
+        <v>103467923</v>
       </c>
       <c r="B12" t="n">
-        <v>78603</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1835,10 +1700,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>733667.458774971</v>
+        <v>733612</v>
       </c>
       <c r="R12" t="n">
-        <v>7366927.369731011</v>
+        <v>7366784</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1868,19 +1733,9 @@
           <t>2022-09-09</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2022-09-09</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1907,19 +1762,14 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>103467941</v>
+        <v>103467925</v>
       </c>
       <c r="B13" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1947,10 +1797,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>733935.4142388134</v>
+        <v>733659</v>
       </c>
       <c r="R13" t="n">
-        <v>7366868.683736058</v>
+        <v>7366865</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1980,19 +1830,9 @@
           <t>2022-09-09</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2022-09-09</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2019,19 +1859,14 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>103467923</v>
+        <v>103467926</v>
       </c>
       <c r="B14" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -2059,10 +1894,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>733612.4244060871</v>
+        <v>733692</v>
       </c>
       <c r="R14" t="n">
-        <v>7366783.515117064</v>
+        <v>7366961</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2092,19 +1927,9 @@
           <t>2022-09-09</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2022-09-09</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2131,32 +1956,27 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>103467949</v>
+        <v>103467928</v>
       </c>
       <c r="B15" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2171,10 +1991,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>733830.4295527732</v>
+        <v>733826</v>
       </c>
       <c r="R15" t="n">
-        <v>7366935.36505157</v>
+        <v>7367017</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2204,19 +2024,9 @@
           <t>2022-09-09</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2022-09-09</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2243,37 +2053,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>103467887</v>
+        <v>103467929</v>
       </c>
       <c r="B16" t="n">
-        <v>95525</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2283,10 +2088,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>733510.4514271568</v>
+        <v>733776</v>
       </c>
       <c r="R16" t="n">
-        <v>7366553.383899614</v>
+        <v>7366967</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2316,19 +2121,9 @@
           <t>2022-09-09</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2022-09-09</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2355,37 +2150,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>103467873</v>
+        <v>103467931</v>
       </c>
       <c r="B17" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2395,10 +2185,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>733789.3613731707</v>
+        <v>733514</v>
       </c>
       <c r="R17" t="n">
-        <v>7366957.756522496</v>
+        <v>7366582</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2428,19 +2218,9 @@
           <t>2022-09-09</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2022-09-09</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2467,19 +2247,14 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>103467931</v>
+        <v>103467933</v>
       </c>
       <c r="B18" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2507,10 +2282,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>733514.0904724016</v>
+        <v>733641</v>
       </c>
       <c r="R18" t="n">
-        <v>7366582.347901474</v>
+        <v>7366644</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2540,19 +2315,9 @@
           <t>2022-09-09</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2022-09-09</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2579,19 +2344,14 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>103467936</v>
+        <v>103467934</v>
       </c>
       <c r="B19" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2619,10 +2379,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>733668.1788085246</v>
+        <v>733668</v>
       </c>
       <c r="R19" t="n">
-        <v>7366740.148728057</v>
+        <v>7366740</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2652,19 +2412,9 @@
           <t>2022-09-09</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2022-09-09</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2691,32 +2441,27 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>103467947</v>
+        <v>103467937</v>
       </c>
       <c r="B20" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2731,10 +2476,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>733847.3875610592</v>
+        <v>733840</v>
       </c>
       <c r="R20" t="n">
-        <v>7367017.507089551</v>
+        <v>7366911</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2764,19 +2509,9 @@
           <t>2022-09-09</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2022-09-09</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2803,32 +2538,27 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>103467948</v>
+        <v>103467939</v>
       </c>
       <c r="B21" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2843,10 +2573,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>733797.6404030685</v>
+        <v>733875</v>
       </c>
       <c r="R21" t="n">
-        <v>7366998.81051076</v>
+        <v>7366887</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2876,19 +2606,9 @@
           <t>2022-09-09</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2022-09-09</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2915,37 +2635,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>103467914</v>
+        <v>103467941</v>
       </c>
       <c r="B22" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2955,10 +2670,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>733600.166259567</v>
+        <v>733935</v>
       </c>
       <c r="R22" t="n">
-        <v>7366727.191707324</v>
+        <v>7366869</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2988,19 +2703,9 @@
           <t>2022-09-09</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2022-09-09</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3027,15 +2732,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>103467880</v>
+        <v>103467873</v>
       </c>
       <c r="B23" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3043,21 +2743,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>6440</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3067,10 +2767,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>733849.4944084208</v>
+        <v>733789</v>
       </c>
       <c r="R23" t="n">
-        <v>7367016.472775252</v>
+        <v>7366958</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -3100,24 +2800,9 @@
           <t>2022-09-09</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2022-09-09</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3144,15 +2829,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>103467926</v>
+        <v>103467914</v>
       </c>
       <c r="B24" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3160,21 +2840,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3184,10 +2864,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>733692.1593946756</v>
+        <v>733600</v>
       </c>
       <c r="R24" t="n">
-        <v>7366960.515189408</v>
+        <v>7366727</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3217,19 +2897,9 @@
           <t>2022-09-09</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2022-09-09</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3256,15 +2926,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>103467899</v>
+        <v>103467915</v>
       </c>
       <c r="B25" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3272,21 +2937,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3296,10 +2961,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>733614.6469986369</v>
+        <v>733621</v>
       </c>
       <c r="R25" t="n">
-        <v>7366853.528082617</v>
+        <v>7366708</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3329,19 +2994,9 @@
           <t>2022-09-09</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2022-09-09</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3368,15 +3023,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>103467904</v>
+        <v>103467895</v>
       </c>
       <c r="B26" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3408,10 +3058,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>733925.4184396311</v>
+        <v>733650</v>
       </c>
       <c r="R26" t="n">
-        <v>7366862.599005624</v>
+        <v>7366828</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3441,19 +3091,9 @@
           <t>2022-09-09</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2022-09-09</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3480,15 +3120,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>103467901</v>
+        <v>103467896</v>
       </c>
       <c r="B27" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3520,10 +3155,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>733721.1516755822</v>
+        <v>733643</v>
       </c>
       <c r="R27" t="n">
-        <v>7366952.044970254</v>
+        <v>7366848</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3553,19 +3188,9 @@
           <t>2022-09-09</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2022-09-09</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3592,15 +3217,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>103467915</v>
+        <v>103467897</v>
       </c>
       <c r="B28" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3608,21 +3228,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3632,10 +3252,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>733621.6059597323</v>
+        <v>733665</v>
       </c>
       <c r="R28" t="n">
-        <v>7366707.592837562</v>
+        <v>7366888</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3665,19 +3285,9 @@
           <t>2022-09-09</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2022-09-09</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3704,37 +3314,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>103467910</v>
+        <v>103467898</v>
       </c>
       <c r="B29" t="n">
-        <v>78603</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3744,10 +3349,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>733923.3114491227</v>
+        <v>733663</v>
       </c>
       <c r="R29" t="n">
-        <v>7366863.633333785</v>
+        <v>7366876</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3777,19 +3382,9 @@
           <t>2022-09-09</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2022-09-09</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3816,15 +3411,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>103467933</v>
+        <v>103467899</v>
       </c>
       <c r="B30" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3832,21 +3422,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3856,10 +3446,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>733641.0844093433</v>
+        <v>733615</v>
       </c>
       <c r="R30" t="n">
-        <v>7366643.83233768</v>
+        <v>7366854</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -3889,19 +3479,9 @@
           <t>2022-09-09</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2022-09-09</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3931,12 +3511,7 @@
         <v>103467900</v>
       </c>
       <c r="B31" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3968,10 +3543,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>733657.630446665</v>
+        <v>733658</v>
       </c>
       <c r="R31" t="n">
-        <v>7366919.282100899</v>
+        <v>7366919</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -4001,19 +3576,9 @@
           <t>2022-09-09</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2022-09-09</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4040,15 +3605,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>103467925</v>
+        <v>103467901</v>
       </c>
       <c r="B32" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4056,21 +3616,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4080,10 +3640,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>733659.3505790499</v>
+        <v>733721</v>
       </c>
       <c r="R32" t="n">
-        <v>7366864.938061805</v>
+        <v>7366952</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -4113,19 +3673,9 @@
           <t>2022-09-09</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2022-09-09</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4152,15 +3702,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>103467921</v>
+        <v>103467902</v>
       </c>
       <c r="B33" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4168,21 +3713,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4192,10 +3737,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>733641.3850557586</v>
+        <v>733641</v>
       </c>
       <c r="R33" t="n">
-        <v>7366645.068445551</v>
+        <v>7366645</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -4225,19 +3770,9 @@
           <t>2022-09-09</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2022-09-09</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4264,15 +3799,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>103467897</v>
+        <v>103467903</v>
       </c>
       <c r="B34" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4304,10 +3834,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>733665.0955728258</v>
+        <v>733657</v>
       </c>
       <c r="R34" t="n">
-        <v>7366888.021476633</v>
+        <v>7366851</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -4337,19 +3867,9 @@
           <t>2022-09-09</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2022-09-09</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4376,15 +3896,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>103467879</v>
+        <v>103467904</v>
       </c>
       <c r="B35" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4392,21 +3907,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4416,10 +3931,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>733621.6059597323</v>
+        <v>733925</v>
       </c>
       <c r="R35" t="n">
-        <v>7366707.592837562</v>
+        <v>7366863</v>
       </c>
       <c r="S35" t="n">
         <v>20</v>
@@ -4449,24 +3964,9 @@
           <t>2022-09-09</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2022-09-09</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Läte</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4493,37 +3993,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>103467882</v>
+        <v>103467876</v>
       </c>
       <c r="B36" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4533,10 +4028,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>733639.9642658294</v>
+        <v>733934</v>
       </c>
       <c r="R36" t="n">
-        <v>7366835.869350312</v>
+        <v>7366870</v>
       </c>
       <c r="S36" t="n">
         <v>20</v>
@@ -4566,19 +4061,9 @@
           <t>2022-09-09</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2022-09-09</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4605,37 +4090,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>103467896</v>
+        <v>103467877</v>
       </c>
       <c r="B37" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4645,10 +4125,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>733642.602727006</v>
+        <v>733668</v>
       </c>
       <c r="R37" t="n">
-        <v>7366847.795189971</v>
+        <v>7366740</v>
       </c>
       <c r="S37" t="n">
         <v>20</v>
@@ -4678,19 +4158,9 @@
           <t>2022-09-09</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2022-09-09</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4717,37 +4187,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>103467937</v>
+        <v>103467878</v>
       </c>
       <c r="B38" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4757,10 +4222,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>733839.6997518977</v>
+        <v>733648</v>
       </c>
       <c r="R38" t="n">
-        <v>7366911.521027</v>
+        <v>7366937</v>
       </c>
       <c r="S38" t="n">
         <v>20</v>
@@ -4790,19 +4255,9 @@
           <t>2022-09-09</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2022-09-09</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4829,32 +4284,27 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>103467939</v>
+        <v>103467944</v>
       </c>
       <c r="B39" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -4869,10 +4319,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>733874.884705894</v>
+        <v>733676</v>
       </c>
       <c r="R39" t="n">
-        <v>7366887.022361287</v>
+        <v>7366931</v>
       </c>
       <c r="S39" t="n">
         <v>20</v>
@@ -4902,19 +4352,9 @@
           <t>2022-09-09</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2022-09-09</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4941,15 +4381,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>103467877</v>
+        <v>103467946</v>
       </c>
       <c r="B40" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4957,21 +4392,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6462</v>
+        <v>6463</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4981,10 +4416,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>733668.1788085246</v>
+        <v>733721</v>
       </c>
       <c r="R40" t="n">
-        <v>7366740.148728057</v>
+        <v>7366952</v>
       </c>
       <c r="S40" t="n">
         <v>20</v>
@@ -5014,19 +4449,9 @@
           <t>2022-09-09</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2022-09-09</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5053,15 +4478,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>103467885</v>
+        <v>103467947</v>
       </c>
       <c r="B41" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5069,21 +4489,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221945</v>
+        <v>6463</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5093,10 +4513,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>733887.6487568578</v>
+        <v>733848</v>
       </c>
       <c r="R41" t="n">
-        <v>7366913.116129208</v>
+        <v>7367017</v>
       </c>
       <c r="S41" t="n">
         <v>20</v>
@@ -5126,19 +4546,9 @@
           <t>2022-09-09</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2022-09-09</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5165,15 +4575,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>103467886</v>
+        <v>103467948</v>
       </c>
       <c r="B42" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5181,21 +4586,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221945</v>
+        <v>6463</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5205,10 +4610,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>733931.2356308398</v>
+        <v>733798</v>
       </c>
       <c r="R42" t="n">
-        <v>7366865.508206568</v>
+        <v>7366999</v>
       </c>
       <c r="S42" t="n">
         <v>20</v>
@@ -5238,19 +4643,9 @@
           <t>2022-09-09</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2022-09-09</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5277,15 +4672,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>103467876</v>
+        <v>103467949</v>
       </c>
       <c r="B43" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5293,21 +4683,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6462</v>
+        <v>6463</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5317,10 +4707,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>733934.4438137778</v>
+        <v>733830</v>
       </c>
       <c r="R43" t="n">
-        <v>7366870.620544679</v>
+        <v>7366935</v>
       </c>
       <c r="S43" t="n">
         <v>20</v>
@@ -5350,19 +4740,9 @@
           <t>2022-09-09</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2022-09-09</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5389,15 +4769,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>103467888</v>
+        <v>103467950</v>
       </c>
       <c r="B44" t="n">
-        <v>95525</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5405,21 +4780,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221941</v>
+        <v>6463</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5429,10 +4804,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>733622.675705696</v>
+        <v>733934</v>
       </c>
       <c r="R44" t="n">
-        <v>7366839.669613218</v>
+        <v>7366870</v>
       </c>
       <c r="S44" t="n">
         <v>20</v>
@@ -5462,19 +4837,9 @@
           <t>2022-09-09</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2022-09-09</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5501,37 +4866,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>103467903</v>
+        <v>103467905</v>
       </c>
       <c r="B45" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5541,10 +4901,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>733656.4786951083</v>
+        <v>733650</v>
       </c>
       <c r="R45" t="n">
-        <v>7366850.974623193</v>
+        <v>7366828</v>
       </c>
       <c r="S45" t="n">
         <v>20</v>
@@ -5574,19 +4934,9 @@
           <t>2022-09-09</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2022-09-09</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5613,15 +4963,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>103467909</v>
+        <v>103467906</v>
       </c>
       <c r="B46" t="n">
-        <v>78603</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5653,10 +4998,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>733798.8456646791</v>
+        <v>733668</v>
       </c>
       <c r="R46" t="n">
-        <v>7366994.068208713</v>
+        <v>7366927</v>
       </c>
       <c r="S46" t="n">
         <v>20</v>
@@ -5686,19 +5031,9 @@
           <t>2022-09-09</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2022-09-09</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5725,37 +5060,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>103467898</v>
+        <v>103467907</v>
       </c>
       <c r="B47" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5765,10 +5095,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>733663.2597488987</v>
+        <v>733719</v>
       </c>
       <c r="R47" t="n">
-        <v>7366876.162940554</v>
+        <v>7366956</v>
       </c>
       <c r="S47" t="n">
         <v>20</v>
@@ -5798,19 +5128,9 @@
           <t>2022-09-09</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2022-09-09</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5837,37 +5157,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>103467874</v>
+        <v>103467908</v>
       </c>
       <c r="B48" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>6464</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5877,10 +5192,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>733910.8976143039</v>
+        <v>733858</v>
       </c>
       <c r="R48" t="n">
-        <v>7366886.406998849</v>
+        <v>7367012</v>
       </c>
       <c r="S48" t="n">
         <v>20</v>
@@ -5910,19 +5225,9 @@
           <t>2022-09-09</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2022-09-09</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5949,37 +5254,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>103467928</v>
+        <v>103467909</v>
       </c>
       <c r="B49" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5989,10 +5289,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>733826.3895849305</v>
+        <v>733799</v>
       </c>
       <c r="R49" t="n">
-        <v>7367017.362566751</v>
+        <v>7366994</v>
       </c>
       <c r="S49" t="n">
         <v>20</v>
@@ -6022,19 +5322,9 @@
           <t>2022-09-09</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2022-09-09</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6061,37 +5351,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>103467895</v>
+        <v>103467910</v>
       </c>
       <c r="B50" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6101,10 +5386,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>733649.8974777906</v>
+        <v>733923</v>
       </c>
       <c r="R50" t="n">
-        <v>7366828.224589536</v>
+        <v>7366864</v>
       </c>
       <c r="S50" t="n">
         <v>20</v>
@@ -6134,19 +5419,9 @@
           <t>2022-09-09</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2022-09-09</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6173,15 +5448,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>103467944</v>
+        <v>103467879</v>
       </c>
       <c r="B51" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6189,21 +5459,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6463</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6213,10 +5483,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>733676.4188347197</v>
+        <v>733621</v>
       </c>
       <c r="R51" t="n">
-        <v>7366931.348607716</v>
+        <v>7366708</v>
       </c>
       <c r="S51" t="n">
         <v>20</v>
@@ -6246,19 +5516,14 @@
           <t>2022-09-09</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2022-09-09</t>
         </is>
       </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Läte</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6285,15 +5550,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>103467905</v>
+        <v>103467880</v>
       </c>
       <c r="B52" t="n">
-        <v>78603</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6301,21 +5561,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6464</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6325,10 +5585,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>733649.8974777906</v>
+        <v>733849</v>
       </c>
       <c r="R52" t="n">
-        <v>7366828.224589536</v>
+        <v>7367017</v>
       </c>
       <c r="S52" t="n">
         <v>20</v>
@@ -6358,19 +5618,14 @@
           <t>2022-09-09</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2022-09-09</t>
         </is>
       </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6397,37 +5652,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>103467929</v>
+        <v>103467875</v>
       </c>
       <c r="B53" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6437,10 +5687,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>733776.0169149707</v>
+        <v>733616</v>
       </c>
       <c r="R53" t="n">
-        <v>7366967.536407137</v>
+        <v>7366873</v>
       </c>
       <c r="S53" t="n">
         <v>20</v>
@@ -6470,19 +5720,14 @@
           <t>2022-09-09</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2022-09-09</t>
         </is>
       </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Två honor</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6509,15 +5754,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>103467883</v>
+        <v>103610635</v>
       </c>
       <c r="B54" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6525,21 +5765,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2081</v>
+        <v>103021</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6549,10 +5789,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>733903.6294359603</v>
+        <v>733599</v>
       </c>
       <c r="R54" t="n">
-        <v>7366920.105702744</v>
+        <v>7366727</v>
       </c>
       <c r="S54" t="n">
         <v>20</v>
@@ -6582,19 +5822,9 @@
           <t>2022-09-09</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2022-09-09</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6621,37 +5851,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>103467884</v>
+        <v>103467913</v>
       </c>
       <c r="B55" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58057</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>221945</v>
+        <v>103031</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6661,10 +5886,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>733607.1373319207</v>
+        <v>733623</v>
       </c>
       <c r="R55" t="n">
-        <v>7366798.410572125</v>
+        <v>7366840</v>
       </c>
       <c r="S55" t="n">
         <v>20</v>
@@ -6694,19 +5919,9 @@
           <t>2022-09-09</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2022-09-09</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6733,37 +5948,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>103610635</v>
+        <v>103467887</v>
       </c>
       <c r="B56" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97989</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103021</v>
+        <v>221941</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6773,10 +5983,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>733599.3301897532</v>
+        <v>733510</v>
       </c>
       <c r="R56" t="n">
-        <v>7366727.52538892</v>
+        <v>7366553</v>
       </c>
       <c r="S56" t="n">
         <v>20</v>
@@ -6806,19 +6016,9 @@
           <t>2022-09-09</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2022-09-09</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6845,37 +6045,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>109911093</v>
+        <v>103467888</v>
       </c>
       <c r="B57" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97989</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1312</v>
+        <v>221941</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6885,13 +6080,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>733661.4335487556</v>
+        <v>733623</v>
       </c>
       <c r="R57" t="n">
-        <v>7366951.081908785</v>
+        <v>7366840</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6915,27 +6110,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2022-10-21</t>
-        </is>
-      </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-09</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2022-10-21</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
+          <t>2022-09-09</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6950,49 +6130,44 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>109911090</v>
+        <v>103467889</v>
       </c>
       <c r="B58" t="n">
-        <v>89952</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97989</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>760</v>
+        <v>221941</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7002,13 +6177,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>733566.8881467576</v>
+        <v>733836</v>
       </c>
       <c r="R58" t="n">
-        <v>7366608.157847239</v>
+        <v>7366914</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7032,27 +6207,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2022-10-21</t>
-        </is>
-      </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-09</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2022-10-21</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
+          <t>2022-09-09</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7067,49 +6227,44 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>109911092</v>
+        <v>103467884</v>
       </c>
       <c r="B59" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>864</v>
+        <v>221945</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7119,13 +6274,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>733661.0994096739</v>
+        <v>733607</v>
       </c>
       <c r="R59" t="n">
-        <v>7366950.246727553</v>
+        <v>7366798</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7149,27 +6304,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2022-10-21</t>
-        </is>
-      </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-09</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2022-10-21</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
+          <t>2022-09-09</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7184,49 +6324,44 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>109911091</v>
+        <v>103467885</v>
       </c>
       <c r="B60" t="n">
-        <v>89952</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>760</v>
+        <v>221945</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7236,13 +6371,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>733554.9189035745</v>
+        <v>733888</v>
       </c>
       <c r="R60" t="n">
-        <v>7366596.661593776</v>
+        <v>7366913</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7266,27 +6401,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2022-10-21</t>
-        </is>
-      </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-09</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2022-10-21</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
+          <t>2022-09-09</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7301,15 +6421,209 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>103467886</v>
+      </c>
+      <c r="B61" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Kåpponis, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>733931</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7366866</v>
+      </c>
+      <c r="S61" t="n">
+        <v>20</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2022-09-09</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2022-09-09</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>103467890</v>
+      </c>
+      <c r="B62" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Kåpponis, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>733621</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7366708</v>
+      </c>
+      <c r="S62" t="n">
+        <v>20</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2022-09-09</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2022-09-09</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 32322-2022 artfynd.xlsx
+++ b/artfynd/A 32322-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY62"/>
+  <dimension ref="A1:AZ62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112605766</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112605767</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103467918</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1075,6 +1095,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112605768</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1172,6 +1197,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103467874</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1269,6 +1299,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103467942</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1371,6 +1406,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112605769</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1468,6 +1508,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103467882</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1565,6 +1610,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103467883</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1662,6 +1712,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103467921</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1759,6 +1814,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103467923</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1856,6 +1916,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103467925</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1953,6 +2018,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103467926</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2050,6 +2120,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103467928</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2147,6 +2222,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103467929</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2244,6 +2324,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103467931</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2341,6 +2426,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103467933</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2438,6 +2528,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103467934</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2535,6 +2630,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103467937</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2632,6 +2732,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103467939</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2729,6 +2834,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103467941</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2826,6 +2936,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103467873</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2923,6 +3038,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103467914</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3020,6 +3140,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103467915</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3117,6 +3242,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103467895</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3214,6 +3344,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103467896</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3311,6 +3446,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103467897</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3408,6 +3548,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103467898</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3505,6 +3650,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103467899</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3602,6 +3752,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103467900</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3699,6 +3854,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103467901</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3796,6 +3956,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103467902</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3893,6 +4058,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103467903</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3990,6 +4160,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103467904</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4087,6 +4262,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103467876</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4184,6 +4364,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103467877</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4281,6 +4466,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103467878</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4378,6 +4568,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103467944</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4475,6 +4670,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103467946</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4572,6 +4772,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103467947</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4669,6 +4874,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103467948</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4766,6 +4976,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103467949</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4863,6 +5078,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103467950</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4960,6 +5180,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103467905</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5057,6 +5282,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103467906</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5154,6 +5384,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103467907</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5251,6 +5486,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103467908</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5348,6 +5588,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103467909</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5445,6 +5690,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103467910</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5547,6 +5797,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103467879</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5649,6 +5904,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103467880</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5751,6 +6011,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103467875</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5848,6 +6113,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103610635</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5945,6 +6215,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103467913</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6042,6 +6317,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103467887</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6139,6 +6419,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103467888</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6236,6 +6521,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103467889</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6333,6 +6623,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103467884</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6430,6 +6725,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103467885</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6527,6 +6827,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103467886</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6624,8 +6929,76 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103467890</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>